--- a/models/sovereigns/Gabon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Gabon_Sovereign_Model.xlsx
@@ -688,16 +688,34 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="n">
+        <v>2.7</v>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -774,16 +792,34 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
+      <c r="B10" s="2" t="n">
+        <v>-10</v>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -856,16 +892,34 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>-4.3</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -873,16 +927,34 @@
           <t>fdi_net_pct_gdp</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>1.768</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -890,16 +962,34 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
+      <c r="B16" s="2" t="n">
+        <v>0.639</v>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -924,16 +1014,34 @@
           <t>import_cover_months</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
+      <c r="B18" s="2" t="n">
+        <v>4.247</v>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>months</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>World Bank WDI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -992,16 +1100,34 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>23.363</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IMF WEO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">

--- a/models/sovereigns/Gabon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Gabon_Sovereign_Model.xlsx
@@ -671,16 +671,34 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>1.597</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IMF CPI database</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08-Oct-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IMF CPI database, all items, y/y % change, monthly (auto-filled; a run's sourced point replaces it unless older)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -750,22 +768,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>latest</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF</t>
+          <t>Fitch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24-May-24</t>
+          <t>22-May-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>public debt near 70% of GDP</t>
+          <t>Total public debt, approximate ('near 70%')</t>
         </is>
       </c>
     </row>
@@ -963,7 +981,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.639</v>
+        <v>0.673</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -972,12 +990,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>IMF International Liquidity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -987,7 +1005,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>Gross official reserves incl. gold at national valuation, end-month (auto-filled; a run's sourced point replaces it unless older)</t>
         </is>
       </c>
     </row>
@@ -1230,11 +1248,6 @@
           <t>CCC-</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>22-May-26</t>
@@ -1278,7 +1291,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (technical surveillance only)</t>
+          <t>None (2021 EFF expired; technical surveillance mission 14-25 Sep-26, no SLA)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Gabon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Gabon_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 08-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/gabon.json</t>
+          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/gabon.json</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fitch</t>
+          <t>Fitch Ratings Sovereign Rating Action on Gabon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CCC-</t>
+          <t>CCC- (LTFC IDR); LTLC CC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (2021 EFF expired; technical surveillance mission 14-25 Sep-26, no SLA)</t>
+          <t>None (2021 EFF expired; Sep-26 staff mission was technical surveillance of the mid-2026 debt audit)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Gabon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Gabon_Sovereign_Model.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>as of 08-Oct-26</t>
+          <t>as of 09-Oct-26</t>
         </is>
       </c>
     </row>
@@ -766,14 +766,10 @@
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>latest</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fitch Ratings Sovereign Rating Action on Gabon</t>
+          <t>Fitch Ratings</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -783,7 +779,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt, approximate ('near 70%')</t>
+          <t>Total public debt, approximate ('near 70% of GDP')</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1241,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CCC- (LTFC IDR); LTLC CC</t>
+          <t>CCC-</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1291,7 +1287,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (2021 EFF expired; Sep-26 staff mission was technical surveillance of the mid-2026 debt audit)</t>
+          <t>None (2021 Extended Fund Facility expired; Sep-26 staff mission ended without a staff-level agreement)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Gabon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Gabon_Sovereign_Model.xlsx
@@ -766,10 +766,14 @@
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fitch Ratings</t>
+          <t>Fitch</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -779,7 +783,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt, approximate ('near 70% of GDP')</t>
+          <t>Total public debt, approximate ("near 70%")</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1291,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (2021 Extended Fund Facility expired; Sep-26 staff mission ended without a staff-level agreement)</t>
+          <t>None (2021 EFF expired); Sep-26 technical surveillance mission only</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Gabon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Gabon_Sovereign_Model.xlsx
@@ -766,24 +766,20 @@
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fitch</t>
+          <t>IMF 2024 Article IV Consultation Staff Report</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22-May-26</t>
+          <t>24-May-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt, approximate ("near 70%")</t>
+          <t>Total public debt, approximate ('near 70%')</t>
         </is>
       </c>
     </row>
@@ -1287,11 +1283,6 @@
       <c r="A33" t="inlineStr">
         <is>
           <t>IMF</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>None (2021 EFF expired); Sep-26 technical surveillance mission only</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Gabon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Gabon_Sovereign_Model.xlsx
@@ -766,20 +766,24 @@
           <t>% GDP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF 2024 Article IV Consultation Staff Report</t>
+          <t>Fitch Sovereign Rating Action on Gabon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24-May-24</t>
+          <t>22-May-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt, approximate ('near 70%')</t>
+          <t>Total public debt, 'near 70% of GDP' (approximate)</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1245,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CCC-</t>
+          <t>CCC- (LTFC IDR); LTLC CC</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1283,6 +1287,11 @@
       <c r="A33" t="inlineStr">
         <is>
           <t>IMF</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>None (2021 Extended Fund Facility expired; Sep-26 staff mission ended without Staff-Level Agreement)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Gabon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Gabon_Sovereign_Model.xlsx
@@ -768,12 +768,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>latest (approximate)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fitch Sovereign Rating Action on Gabon</t>
+          <t>Fitch Ratings Sovereign Rating Action on Gabon</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Total public debt, 'near 70% of GDP' (approximate)</t>
+          <t>Total public debt, approximate ("near 70% of GDP")</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CCC- (LTFC IDR); LTLC CC</t>
+          <t>CCC-</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>None (2021 Extended Fund Facility expired; Sep-26 staff mission ended without Staff-Level Agreement)</t>
+          <t>None (2021 Extended Fund Facility expired; Sep-26 staff mission was surveillance only)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Gabon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Gabon_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/gabon.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/gabon.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Gabon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Gabon_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/gabon.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/gabon.json</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>08-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/models/sovereigns/Gabon_Sovereign_Model.xlsx
+++ b/models/sovereigns/Gabon_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/gabon.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/gabon.json</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
